--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20232.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -74,6 +74,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>GUERRA</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>CLAUDIA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -591,16 +600,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -614,16 +626,19 @@
         <v>34</v>
       </c>
       <c r="D3">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>34</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>79.41</v>
+      </c>
+      <c r="H3">
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -637,16 +652,19 @@
         <v>45</v>
       </c>
       <c r="D4">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>95.56</v>
+      </c>
+      <c r="H4">
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -702,16 +720,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="G2">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -728,16 +746,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="F3">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>97.06</v>
+        <v>79.41</v>
       </c>
       <c r="H3">
-        <v>7.6</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -754,16 +772,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G4">
-        <v>97.78</v>
+        <v>95.56</v>
       </c>
       <c r="H4">
-        <v>7.9</v>
+        <v>7.6</v>
       </c>
     </row>
   </sheetData>
@@ -773,7 +791,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -803,6 +821,29 @@
         <v>18</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920212</v>
+      </c>
+      <c r="B2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20232.xlsx
+++ b/docentes/Mendoza Velazquez Laura Elena - Estadisticos 20232.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -74,15 +74,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>CLAUDIA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -720,16 +711,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="H2">
-        <v>7.9</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -746,16 +737,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>79.41</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -772,16 +763,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G4">
-        <v>95.56</v>
+        <v>97.78</v>
       </c>
       <c r="H4">
-        <v>7.6</v>
+        <v>7.9</v>
       </c>
     </row>
   </sheetData>
@@ -791,7 +782,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -821,29 +812,6 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920212</v>
-      </c>
-      <c r="B2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
